--- a/automotive_forms/007_vehicle_safety_assessment_form--automotive_forms.xlsx
+++ b/automotive_forms/007_vehicle_safety_assessment_form--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'airbag'}</t>
+          <t>airbag</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Airbag'}</t>
+          <t>Airbag</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'anti-lock_braking_system'}</t>
+          <t>anti-lock_braking_system</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Anti-lock Braking System'}</t>
+          <t>Anti-lock Braking System</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'electronic_stability_control'}</t>
+          <t>electronic_stability_control</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Electronic Stability Control'}</t>
+          <t>Electronic Stability Control</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'certified'}</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Certified'}</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_certified'}</t>
+          <t>not_certified</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not Certified'}</t>
+          <t>Not Certified</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fire_suppression_system'}</t>
+          <t>fire_suppression_system</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fire Suppression System'}</t>
+          <t>Fire Suppression System</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'emergency_exit_signs'}</t>
+          <t>emergency_exit_signs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Emergency Exit Signs'}</t>
+          <t>Emergency Exit Signs</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'required'}</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Required'}</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'recommended'}</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Recommended'}</t>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'replace'}</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Replace'}</t>
+          <t>Replace</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'repair'}</t>
+          <t>repair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Repair'}</t>
+          <t>Repair</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'inspect'}</t>
+          <t>inspect</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Inspect'}</t>
+          <t>Inspect</t>
         </is>
       </c>
     </row>
